--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_wearing_bar.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_wearing_bar.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25065" windowHeight="12360"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_wearing_bar" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="55">
   <si>
     <t>穿戴栏id</t>
   </si>
@@ -53,8 +53,47 @@
     <t>用于标识穿戴栏类别；新增特殊作用标签需要额外处理</t>
   </si>
   <si>
-    <t>填写引用文件名称，不填则不显示
-格式：穿戴栏图标#穿戴栏文本</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>填写引用文件名称，不填则不显示</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>格式：穿戴栏图标</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>穿戴栏文本</t>
+    </r>
   </si>
   <si>
     <t>穿戴栏部位根据界面显示开放，填写穿戴栏要隐藏的部位；读取cfg_item表strPart部位</t>
@@ -96,7 +135,7 @@
     <t>zb_01</t>
   </si>
   <si>
-    <t>16#17#19#101#102#103#104#105#106#107#108#109#110#111#112#113#114#115#116#117#71#72#73#74#75#76#77#78</t>
+    <t>16#17#101#102#103#104#105#106#107#108#109#110#111#112#113#114#115#116#117#71#72#73#74#75#76#77#78</t>
   </si>
   <si>
     <t>2</t>
@@ -193,9 +232,6 @@
   </si>
   <si>
     <t>基础穿戴栏</t>
-  </si>
-  <si>
-    <t>16#17#101#102#103#104#105#106#107#108#109#110#111#112#113#114#115#116</t>
   </si>
 </sst>
 </file>
@@ -819,12 +855,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1386,7 +1425,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="1" spans="1:5">
+    <row r="2" customFormat="1" ht="111" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1396,7 +1435,7 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E2" t="s">
@@ -1438,7 +1477,7 @@
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B5" t="s">
@@ -1455,7 +1494,7 @@
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:5">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1472,7 +1511,7 @@
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:5">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1489,7 +1528,7 @@
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:5">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>30</v>
       </c>
       <c r="B8" t="s">
@@ -1506,7 +1545,7 @@
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:5">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B9" t="s">
@@ -1523,7 +1562,7 @@
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:5">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>36</v>
       </c>
       <c r="B10" t="s">
@@ -1540,7 +1579,7 @@
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:5">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B11" t="s">
@@ -1557,7 +1596,7 @@
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:5">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B12" t="s">
@@ -1574,7 +1613,7 @@
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:5">
-      <c r="A13" s="3">
+      <c r="A13" s="4">
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1591,7 +1630,7 @@
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:5">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1608,7 +1647,7 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="3">
+      <c r="A15" s="4">
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1634,8 +1673,9 @@
       <c r="C16" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_wearing_bar.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_wearing_bar.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_wearing_bar" sheetId="1" r:id="rId1"/>
@@ -1404,7 +1404,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="25.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="9.28571428571429" customWidth="1"/>
+    <col min="2" max="2" width="19.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="20.8571428571429" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
     <col min="5" max="5" width="19.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
